--- a/resources/Template.xlsx
+++ b/resources/Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8555" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Quota" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
     <t xml:space="preserve"> Envíar el comprobante al correo impresionescaptis@gmail.com o al número de whatsapp 4493931290. Favor de enviar los datos de facturación al correo, si se necesita y comprobantes de los pagos al correo: impresionescaptis@gmail.com.  El tiempo de entrega y disponibilidad de colores puede variar según la carga de trabajo y de nuestros provedores.</t>
   </si>
   <si>
-    <t>Ubicaciones</t>
+    <t>Ubicaciones y horarios</t>
   </si>
   <si>
     <t>Datos bancarios</t>
@@ -153,7 +153,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>646017206800021346</t>
+      <t>722969010700021345</t>
     </r>
     <r>
       <rPr>
@@ -222,7 +222,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Sabado</t>
+      <t>Sábado</t>
     </r>
     <r>
       <rPr>
@@ -236,7 +236,7 @@
     </r>
   </si>
   <si>
-    <t>PUNTOS DE ENTREGA CON PREVIA CITA</t>
+    <t>PUNTOS DE ENTREGA CON CITA PREVIA</t>
   </si>
   <si>
     <t>📍 Plaza Kune</t>
@@ -246,6 +246,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Lunes a Viernes</t>
     </r>
     <r>
@@ -267,7 +275,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Sabado</t>
+      <t>Sábado</t>
     </r>
     <r>
       <rPr>
@@ -331,7 +339,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="45">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,13 +416,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="0" tint="-0.499984740745262"/>
@@ -423,6 +424,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1" tint="0.0499893185216834"/>
@@ -520,13 +528,6 @@
     </font>
     <font>
       <sz val="26"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1302,150 +1303,150 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1521,18 +1522,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1544,19 +1548,16 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1615,16 +1616,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1647,10 +1648,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1663,13 +1660,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2470,178 +2461,178 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.4" spans="1:8">
-      <c r="A1" s="105"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108" t="s">
+      <c r="A1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="109"/>
-      <c r="H1" s="104"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="98"/>
     </row>
     <row r="2" ht="54.75" customHeight="1" spans="1:8">
-      <c r="A2" s="110"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="108" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="113"/>
-      <c r="H2" s="104"/>
-    </row>
-    <row r="3" s="103" customFormat="1" spans="1:9">
-      <c r="A3" s="108" t="s">
+      <c r="G2" s="107"/>
+      <c r="H2" s="98"/>
+    </row>
+    <row r="3" s="97" customFormat="1" spans="1:9">
+      <c r="A3" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="108" t="s">
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="109" t="s">
+      <c r="G3" s="103" t="s">
         <v>4</v>
       </c>
       <c r="I3"/>
     </row>
-    <row r="4" s="103" customFormat="1" spans="1:11">
-      <c r="A4" s="108" t="s">
+    <row r="4" s="97" customFormat="1" spans="1:11">
+      <c r="A4" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="115"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="108" t="s">
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="109" t="s">
+      <c r="G4" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="127"/>
+      <c r="K4" s="127"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="116"/>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="118"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="112"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="119"/>
-      <c r="B6" s="120"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="121"/>
+      <c r="A6" s="113"/>
+      <c r="B6" s="114"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="115"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="119"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="121"/>
+      <c r="A7" s="113"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="115"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="121"/>
+      <c r="A8" s="113"/>
+      <c r="B8" s="114"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="114"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="115"/>
     </row>
     <row r="9" ht="61.15" customHeight="1" spans="1:11">
-      <c r="A9" s="122"/>
-      <c r="B9" s="123"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="123"/>
-      <c r="F9" s="123"/>
-      <c r="G9" s="124"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="134"/>
+      <c r="A9" s="116"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="118"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="128"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="125" t="s">
+      <c r="A10" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-    </row>
-    <row r="11" s="104" customFormat="1" spans="1:7">
-      <c r="A11" s="104" t="s">
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+    </row>
+    <row r="11" s="98" customFormat="1" spans="1:7">
+      <c r="A11" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="104" t="s">
+      <c r="D11" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="104" t="s">
+      <c r="E11" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="126" t="s">
+      <c r="F11" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="127" t="s">
+      <c r="G11" s="121" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" s="103" customFormat="1" spans="1:10">
-      <c r="A12" s="128"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="130" t="s">
+    <row r="12" s="97" customFormat="1" spans="1:10">
+      <c r="A12" s="122"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="129"/>
-      <c r="J12" s="104"/>
+      <c r="G12" s="123"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" ht="14.45" customHeight="1" spans="1:7">
-      <c r="A13" s="119"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="120"/>
-      <c r="G13" s="131"/>
+      <c r="A13" s="113"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="114"/>
+      <c r="G13" s="125"/>
     </row>
     <row r="14" ht="14.45" customHeight="1"/>
     <row r="29" ht="14.45" customHeight="1"/>
     <row r="34" spans="8:8">
-      <c r="H34" s="132"/>
+      <c r="H34" s="126"/>
     </row>
     <row r="35" spans="8:8">
-      <c r="H35" s="132"/>
+      <c r="H35" s="126"/>
     </row>
     <row r="36" spans="8:8">
-      <c r="H36" s="132"/>
+      <c r="H36" s="126"/>
     </row>
     <row r="37" spans="8:8">
-      <c r="H37" s="132"/>
+      <c r="H37" s="126"/>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" s="132"/>
+      <c r="H38" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2651,7 +2642,7 @@
     <mergeCell ref="A5:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" scale="93" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="1" scale="80" fitToHeight="0" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
@@ -2858,9 +2849,9 @@
       <c r="B15" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="25"/>
       <c r="G15" s="26"/>
       <c r="L15" s="72"/>
@@ -2870,11 +2861,11 @@
       <c r="P15" s="74"/>
     </row>
     <row r="16" ht="14.45" customHeight="1" spans="1:16">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="32"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="25"/>
       <c r="G16" s="26"/>
       <c r="L16" s="78"/>
@@ -2884,20 +2875,20 @@
       <c r="P16" s="72"/>
     </row>
     <row r="17" ht="14.45" customHeight="1" spans="1:16">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="25"/>
       <c r="G17" s="26"/>
-      <c r="L17" s="81"/>
+      <c r="L17" s="78"/>
       <c r="M17" s="79"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="83"/>
-      <c r="P17" s="84"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="80"/>
+      <c r="P17" s="77"/>
     </row>
     <row r="18" ht="14.45" customHeight="1" spans="1:16">
       <c r="A18" s="17" t="s">
@@ -2911,11 +2902,11 @@
       <c r="E18" s="19"/>
       <c r="F18" s="25"/>
       <c r="G18" s="26"/>
-      <c r="L18" s="81"/>
+      <c r="L18" s="78"/>
       <c r="M18" s="79"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="84"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="77"/>
     </row>
     <row r="19" ht="14.45" customHeight="1" spans="1:16">
       <c r="A19" s="22"/>
@@ -2925,29 +2916,29 @@
       <c r="E19" s="24"/>
       <c r="F19" s="25"/>
       <c r="G19" s="26"/>
-      <c r="L19" s="81"/>
+      <c r="L19" s="78"/>
       <c r="M19" s="79"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="84"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="77"/>
     </row>
     <row r="20" ht="14.45" customHeight="1" spans="1:16">
       <c r="A20" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="37"/>
       <c r="F20" s="25"/>
       <c r="G20" s="26"/>
-      <c r="L20" s="81"/>
+      <c r="L20" s="78"/>
       <c r="M20" s="79"/>
-      <c r="N20" s="82"/>
-      <c r="O20" s="83"/>
-      <c r="P20" s="84"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="77"/>
     </row>
     <row r="21" ht="14.45" customHeight="1" spans="1:16">
       <c r="A21" s="17" t="s">
@@ -2961,11 +2952,11 @@
       <c r="E21" s="19"/>
       <c r="F21" s="25"/>
       <c r="G21" s="26"/>
-      <c r="L21" s="81"/>
+      <c r="L21" s="78"/>
       <c r="M21" s="79"/>
-      <c r="N21" s="82"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="84"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="77"/>
     </row>
     <row r="22" ht="14.45" customHeight="1" spans="1:16">
       <c r="A22" s="22"/>
@@ -2975,11 +2966,11 @@
       <c r="E22" s="24"/>
       <c r="F22" s="25"/>
       <c r="G22" s="26"/>
-      <c r="L22" s="81"/>
+      <c r="L22" s="78"/>
       <c r="M22" s="79"/>
-      <c r="N22" s="82"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="84"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="77"/>
     </row>
     <row r="23" ht="14.45" customHeight="1" spans="1:16">
       <c r="A23" s="38" t="s">
@@ -2993,11 +2984,11 @@
       <c r="E23" s="40"/>
       <c r="F23" s="25"/>
       <c r="G23" s="26"/>
-      <c r="L23" s="81"/>
+      <c r="L23" s="78"/>
       <c r="M23" s="79"/>
-      <c r="N23" s="82"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="84"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="77"/>
     </row>
     <row r="24" ht="14.45" customHeight="1" spans="1:16">
       <c r="A24" s="17" t="s">
@@ -3011,11 +3002,11 @@
       <c r="E24" s="19"/>
       <c r="F24" s="25"/>
       <c r="G24" s="26"/>
-      <c r="L24" s="81"/>
+      <c r="L24" s="78"/>
       <c r="M24" s="79"/>
-      <c r="N24" s="82"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="84"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="77"/>
     </row>
     <row r="25" ht="14.45" customHeight="1" spans="1:16">
       <c r="A25" s="22"/>
@@ -3025,11 +3016,11 @@
       <c r="E25" s="24"/>
       <c r="F25" s="25"/>
       <c r="G25" s="26"/>
-      <c r="L25" s="81"/>
+      <c r="L25" s="78"/>
       <c r="M25" s="79"/>
-      <c r="N25" s="82"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="84"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="77"/>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="38" t="s">
@@ -3043,27 +3034,27 @@
       <c r="E26" s="40"/>
       <c r="F26" s="25"/>
       <c r="G26" s="26"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="86"/>
+      <c r="L26" s="81"/>
+      <c r="M26" s="82"/>
       <c r="N26" s="74"/>
-      <c r="O26" s="87"/>
-      <c r="P26" s="88"/>
+      <c r="O26" s="83"/>
+      <c r="P26" s="84"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="35"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
       <c r="F27" s="25"/>
       <c r="G27" s="26"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="89"/>
-      <c r="N27" s="82"/>
-      <c r="O27" s="90"/>
-      <c r="P27" s="91"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="84"/>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="38" t="s">
@@ -3077,11 +3068,11 @@
       <c r="E28" s="40"/>
       <c r="F28" s="41"/>
       <c r="G28" s="42"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="82"/>
-      <c r="O28" s="90"/>
-      <c r="P28" s="91"/>
+      <c r="L28" s="81"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="84"/>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="43" t="s">
@@ -3095,11 +3086,11 @@
         <v>42</v>
       </c>
       <c r="G29" s="12"/>
-      <c r="L29" s="92"/>
-      <c r="M29" s="93"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="87"/>
       <c r="N29" s="72"/>
-      <c r="O29" s="94"/>
-      <c r="P29" s="94"/>
+      <c r="O29" s="88"/>
+      <c r="P29" s="88"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="46" t="s">
@@ -3115,10 +3106,10 @@
       <c r="G30" s="51"/>
       <c r="L30" s="75"/>
       <c r="M30" s="72"/>
-      <c r="N30" s="95"/>
-      <c r="O30" s="96"/>
-      <c r="P30" s="96"/>
-      <c r="Q30" s="102"/>
+      <c r="N30" s="89"/>
+      <c r="O30" s="90"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="96"/>
     </row>
     <row r="31" ht="18" spans="1:17">
       <c r="A31" s="52" t="s">
@@ -3135,10 +3126,10 @@
       <c r="G31" s="57"/>
       <c r="L31" s="75"/>
       <c r="M31" s="72"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="102"/>
+      <c r="N31" s="91"/>
+      <c r="O31" s="92"/>
+      <c r="P31" s="93"/>
+      <c r="Q31" s="96"/>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="58"/>
@@ -3151,11 +3142,11 @@
       <c r="E32" s="55"/>
       <c r="F32" s="56"/>
       <c r="G32" s="57"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="101"/>
-      <c r="N32" s="101"/>
-      <c r="O32" s="101"/>
-      <c r="P32" s="102"/>
+      <c r="L32" s="94"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="95"/>
+      <c r="O32" s="95"/>
+      <c r="P32" s="96"/>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="59"/>
@@ -3202,13 +3193,13 @@
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A6:G10"/>
     <mergeCell ref="B13:E14"/>
-    <mergeCell ref="A6:G10"/>
+    <mergeCell ref="F13:G28"/>
     <mergeCell ref="B18:E19"/>
     <mergeCell ref="B21:E22"/>
     <mergeCell ref="B24:E25"/>
     <mergeCell ref="F30:G34"/>
-    <mergeCell ref="F13:G28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A34" r:id="rId2" display="Política de pivacidad"/>
